--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_22_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_22_R3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7644</v>
+        <v>3.1109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8442</v>
+        <v>0.3483</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9202</v>
+        <v>2.7627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7566000000000001</v>
+        <v>-0.1822</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.468</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2246</v>
+        <v>0.5119</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5435</v>
+        <v>-0.0459</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2086</v>
+        <v>-0.6681</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3349</v>
+        <v>0.6222</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7869</v>
+        <v>-0.1363</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6766</v>
+        <v>-0.026</v>
       </c>
       <c r="O2" t="n">
         <v>-0.1103</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9923999999999999</v>
+        <v>-0.0806</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6994</v>
+        <v>0.0358</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6918</v>
+        <v>-0.1164</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5361</v>
+        <v>1.7501</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6932</v>
+        <v>3.0309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8633</v>
+        <v>1.191</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8299</v>
+        <v>1.8399</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1822</v>
+        <v>2.1592</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6941000000000001</v>
+        <v>0.2185</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5119</v>
+        <v>1.9407</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0459</v>
+        <v>2.8743</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6681</v>
+        <v>0.7163</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6222</v>
+        <v>2.1581</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1363</v>
+        <v>-0.7151</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.026</v>
+        <v>-0.4978</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1103</v>
+        <v>-0.2173</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5017</v>
+        <v>-0.2005</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.2041</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0492</v>
+        <v>0.0035</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5426</v>
+        <v>2.645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7054</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1592</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2185</v>
+        <v>-0.468</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9407</v>
+        <v>1.2246</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8743</v>
+        <v>1.5435</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7163</v>
+        <v>0.2086</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1581</v>
+        <v>1.3349</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7151</v>
+        <v>-0.7869</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4978</v>
+        <v>-0.6766</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2173</v>
+        <v>-0.1103</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6888</v>
+        <v>-0.127</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5579</v>
+        <v>-0.9785</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1309</v>
+        <v>0.8516</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.171</v>
+        <v>2.0936</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9509</v>
+        <v>-0.6052</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2202</v>
+        <v>2.6988</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5463</v>
+        <v>2.546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.5149</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3986</v>
+        <v>2.0311</v>
       </c>
       <c r="J5" t="n">
-        <v>0.215</v>
+        <v>1.7566</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9278</v>
+        <v>-0.1205</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7127</v>
+        <v>1.8771</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7613</v>
+        <v>0.7894</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0755</v>
+        <v>0.6354</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6859</v>
+        <v>0.154</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>3.2473</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3926</v>
+        <v>-0.6664</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5192</v>
+        <v>-0.4007</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8733</v>
+        <v>-0.2658</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3247</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6083</v>
+        <v>1.7501</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9517</v>
+        <v>1.8007</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6798999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6315</v>
+        <v>1.0857</v>
       </c>
       <c r="G6" t="n">
-        <v>2.546</v>
+        <v>-0.5463</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5149</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0311</v>
+        <v>-1.3986</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7566</v>
+        <v>0.215</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1205</v>
+        <v>0.9278</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8771</v>
+        <v>-0.7127</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7894</v>
+        <v>-0.7613</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6354</v>
+        <v>-0.0755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.154</v>
+        <v>-0.6859</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2473</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8083</v>
+        <v>1.0222</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4753</v>
+        <v>0.2833</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.333</v>
+        <v>0.7389</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.3247</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7501</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7257</v>
+        <v>-0.9534</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1845</v>
+        <v>-1.1098</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4589</v>
+        <v>0.1564</v>
       </c>
       <c r="G7" t="n">
         <v>-0.191</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6278</v>
+        <v>0.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0316</v>
+        <v>0.1063</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5961</v>
+        <v>0.2937</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9304</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SAMANIC</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6859</v>
+        <v>-1.2448</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3091</v>
+        <v>-4.3063</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3768</v>
+        <v>3.0615</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.107</v>
+        <v>-1.3417</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>1.0039</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2643</v>
+        <v>-2.3456</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-2.278</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.4461</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.107</v>
+        <v>0.9363</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>0.8358</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2643</v>
+        <v>0.1005</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.0154</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4191</v>
+        <v>-1.6168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>-0.8685</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2697</v>
+        <v>-0.7483</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9246</v>
+        <v>-1.2848</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4102</v>
+        <v>-3.9384</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4856</v>
+        <v>2.6537</v>
       </c>
       <c r="G9" t="n">
         <v>0.6645</v>
@@ -1156,13 +1156,13 @@
         <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0556</v>
+        <v>-0.4158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9709</v>
+        <v>-0.4991</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0848</v>
+        <v>0.0833</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>L. SAMANIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.925</v>
+        <v>-1.6187</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6169</v>
+        <v>-1.3091</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6919</v>
+        <v>-0.3095</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3417</v>
+        <v>-0.107</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0039</v>
+        <v>0.1573</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3456</v>
+        <v>-0.2643</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.278</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.168</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4461</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9363</v>
+        <v>-0.107</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8358</v>
+        <v>0.1573</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1005</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0154</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2971</v>
+        <v>-0.3519</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1791</v>
+        <v>-0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.118</v>
+        <v>-0.2025</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6645</v>
+        <v>-2.4965</v>
       </c>
       <c r="E11" t="n">
         <v>-1.6396</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0249</v>
+        <v>-0.8568</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5503</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2082</v>
       </c>
       <c r="U11" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5196</v>
+        <v>-4.032</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.654</v>
+        <v>-4.536</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1343</v>
+        <v>0.504</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2616</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8817</v>
+        <v>-0.3941</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5737</v>
+        <v>-0.4558</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3079</v>
+        <v>0.0617</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6776000000000009</v>
+        <v>1.0509</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.9986</v>
+        <v>-14.6251</v>
       </c>
       <c r="F13" t="n">
-        <v>15.6762</v>
+        <v>15.6764</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0538</v>
@@ -1468,13 +1468,13 @@
         <v>20.8757</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7323</v>
+        <v>-2.3591</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7122</v>
+        <v>-3.3389</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9796999999999996</v>
+        <v>0.9798000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4708</v>
+        <v>6.493</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8725</v>
+        <v>2.1084</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5983</v>
+        <v>4.3846</v>
       </c>
       <c r="G14" t="n">
         <v>5.8343</v>
@@ -1546,13 +1546,13 @@
         <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6133</v>
+        <v>1.6355</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0703</v>
+        <v>0.1656</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6836</v>
+        <v>1.4699</v>
       </c>
       <c r="V14" t="n">
         <v>0.6468</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5083</v>
+        <v>3.133</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0258</v>
+        <v>0.2002</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4825</v>
+        <v>2.9328</v>
       </c>
       <c r="G15" t="n">
         <v>0.1374</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6904</v>
+        <v>1.315</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6414</v>
+        <v>-0.1843</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0491</v>
+        <v>1.4993</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0117</v>
+        <v>2.8613</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8748</v>
+        <v>-1.7426</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1369</v>
+        <v>4.6039</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2277</v>
+        <v>3.9365</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5955</v>
+        <v>1.7851</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8231000000000001</v>
+        <v>2.1514</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7735</v>
+        <v>3.8549</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6469</v>
+        <v>2.3261</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8734</v>
+        <v>1.5289</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0012</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0514</v>
+        <v>-0.5409</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0502</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-5.7988</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>3.2473</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2394</v>
+        <v>1.4763</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1889</v>
+        <v>0.0595</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0505</v>
+        <v>1.4168</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7884</v>
+        <v>2.2616</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0964</v>
+        <v>-1.0243</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8848</v>
+        <v>3.2859</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9365</v>
+        <v>-0.2203</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7851</v>
+        <v>-2.2246</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1514</v>
+        <v>2.0043</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8549</v>
+        <v>-0.6238</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3261</v>
+        <v>-1.9487</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5289</v>
+        <v>1.325</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.4035</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5409</v>
+        <v>-0.2759</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6793</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2473</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4033</v>
+        <v>0.2526</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2943</v>
+        <v>-0.5423</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6976</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1335</v>
+        <v>1.9502</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3782</v>
+        <v>0.7569</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5117</v>
+        <v>1.1934</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2203</v>
+        <v>-0.2277</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2246</v>
+        <v>0.5955</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0043</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6238</v>
+        <v>0.7735</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9487</v>
+        <v>1.6469</v>
       </c>
       <c r="L18" t="n">
-        <v>1.325</v>
+        <v>-0.8734</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4035</v>
+        <v>-1.0012</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2759</v>
+        <v>-1.0514</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6793</v>
+        <v>0.0502</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8754999999999999</v>
+        <v>0.1779</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>0.0709</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0207</v>
+        <v>0.107</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3406</v>
+        <v>0.5486</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0752</v>
+        <v>0.0428</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4158</v>
+        <v>0.5058</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3851</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.434</v>
+        <v>-0.226</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0141</v>
+        <v>0.1041</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1188</v>
+        <v>0.0008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1896</v>
+        <v>0.0716</v>
       </c>
       <c r="F20" t="n">
         <v>-0.0708</v>
@@ -2014,10 +2014,10 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4233</v>
+        <v>1.3054</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0499</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>0.3734</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3093</v>
+        <v>-0.2421</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1326</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1768</v>
+        <v>-0.1095</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2048</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1046</v>
+        <v>-0.0373</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0746</v>
+        <v>-2.5559</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1903</v>
+        <v>-4.1339</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1157</v>
+        <v>1.578</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6021</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2439</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0499</v>
+        <v>0.1063</v>
       </c>
       <c r="U22" t="n">
-        <v>1.194</v>
+        <v>0.6563</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7886</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1206</v>
+        <v>-3.1818</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3692</v>
+        <v>-3.6538</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2486</v>
+        <v>0.472</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2634</v>
+        <v>-0.7177</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4598</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8036</v>
+        <v>-0.0467</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4626</v>
+        <v>0.2261</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7661</v>
+        <v>-0.3627</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6965</v>
+        <v>0.5889</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8008</v>
+        <v>-0.9438</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6938</v>
+        <v>-0.3082</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.107</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5531</v>
+        <v>-0.2348</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7468</v>
+        <v>-0.4007</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1937</v>
+        <v>0.1658</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5339</v>
+        <v>-3.8004</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1916</v>
+        <v>-4.0153</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3423</v>
+        <v>0.2149</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3211</v>
+        <v>-3.2634</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5054</v>
+        <v>-1.4598</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8265</v>
+        <v>-1.8036</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2827</v>
+        <v>-2.4626</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.43</v>
+        <v>-0.7661</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1472</v>
+        <v>-1.6965</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6039</v>
+        <v>-0.8008</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0755</v>
+        <v>-0.6938</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6793</v>
+        <v>-0.107</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1502</v>
+        <v>-0.2328</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0395</v>
+        <v>-0.393</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1107</v>
+        <v>0.1601</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.5413</v>
+        <v>-0.5361</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.7527</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0113</v>
+        <v>-4.2143</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5974</v>
+        <v>-2.5454</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4139</v>
+        <v>-1.6688</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7177</v>
+        <v>0.3211</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.5054</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0467</v>
+        <v>0.8265</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2261</v>
+        <v>-0.2827</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3627</v>
+        <v>-0.43</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5889</v>
+        <v>0.1472</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9438</v>
+        <v>0.6039</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3082</v>
+        <v>-0.0755</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.6793</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0643</v>
+        <v>0.4698</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3443</v>
+        <v>-0.3143</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.72</v>
+        <v>0.7842</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1418</v>
+        <v>-4.5413</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1418</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="26">
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6776000000000009</v>
+        <v>3.254</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.0682</v>
+        <v>-14.068</v>
       </c>
       <c r="F26" t="n">
-        <v>13.3905</v>
+        <v>17.3222</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0537</v>
+        <v>1.053700000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.358899999999999</v>
+        <v>-2.3589</v>
       </c>
       <c r="I26" t="n">
-        <v>3.412900000000001</v>
+        <v>3.4129</v>
       </c>
       <c r="J26" t="n">
-        <v>2.647799999999998</v>
+        <v>2.647799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2937</v>
+        <v>1.293700000000001</v>
       </c>
       <c r="L26" t="n">
         <v>1.3543</v>
@@ -2467,7 +2467,7 @@
         <v>-1.594</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.652799999999999</v>
+        <v>-3.6528</v>
       </c>
       <c r="O26" t="n">
         <v>2.0587</v>
@@ -2482,19 +2482,19 @@
         <v>18.5563</v>
       </c>
       <c r="S26" t="n">
-        <v>2.732300000000001</v>
+        <v>6.664199999999999</v>
       </c>
       <c r="T26" t="n">
         <v>-0.9798</v>
       </c>
       <c r="U26" t="n">
-        <v>3.712199999999999</v>
+        <v>7.6438</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1444</v>
       </c>
       <c r="W26" t="n">
-        <v>5.139600000000002</v>
+        <v>5.139600000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-7.284</v>
